--- a/backtest_runs/20260410_193731/by_symbol/FIBLM/FIBLM.xlsx
+++ b/backtest_runs/20260410_193731/by_symbol/FIBLM/FIBLM.xlsx
@@ -465,12 +465,12 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>same_side_as_oracle</t>
+          <t>same_side_as_actual</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_diff_oracle_minus_model</t>
+          <t>daily_pnl_diff_actual_minus_model</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -480,7 +480,7 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>suggestion_oracle</t>
+          <t>suggestion_actual</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -490,7 +490,7 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_oracle</t>
+          <t>daily_pnl_actual</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
@@ -500,7 +500,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>equity_oracle</t>
+          <t>equity_actual</t>
         </is>
       </c>
     </row>
@@ -633,7 +633,7 @@
         <v>-6990</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K4" s="3" t="n">
         <v>102423.2</v>
@@ -725,7 +725,7 @@
         <v>-3261.999999999997</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K6" s="3" t="n">
         <v>102702.8</v>
@@ -771,7 +771,7 @@
         <v>-2330</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K7" s="3" t="n">
         <v>100372.8</v>
@@ -863,7 +863,7 @@
         <v>-279.5999999999941</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K9" s="3" t="n">
         <v>103728</v>
@@ -909,7 +909,7 @@
         <v>-4287.200000000008</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K10" s="3" t="n">
         <v>99440.79999999999</v>
@@ -1231,7 +1231,7 @@
         <v>-12675.20000000001</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K17" s="3" t="n">
         <v>120690.4</v>
@@ -1277,7 +1277,7 @@
         <v>-11463.59999999999</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K18" s="3" t="n">
         <v>109226.8</v>
@@ -1323,7 +1323,7 @@
         <v>-186.4000000000126</v>
       </c>
       <c r="J19" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K19" s="3" t="n">
         <v>109040.4</v>
@@ -1415,7 +1415,7 @@
         <v>-93.19999999999801</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K21" s="3" t="n">
         <v>109692.8</v>
@@ -1461,7 +1461,7 @@
         <v>-931.9999999999967</v>
       </c>
       <c r="J22" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K22" s="3" t="n">
         <v>108760.8</v>
@@ -1553,7 +1553,7 @@
         <v>-279.5999999999941</v>
       </c>
       <c r="J24" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K24" s="3" t="n">
         <v>110718</v>
